--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.22026</v>
+        <v>17.01065</v>
       </c>
       <c r="D2" t="n">
-        <v>16.27637</v>
+        <v>16.65893</v>
       </c>
       <c r="E2" t="n">
-        <v>16.98994</v>
+        <v>16.71231</v>
       </c>
       <c r="F2" t="n">
-        <v>42.60568</v>
+        <v>41.61183</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05043</v>
+        <v>0.04959</v>
       </c>
       <c r="H2" t="n">
-        <v>1.77749</v>
+        <v>1.8184</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.91924</v>
+        <v>16.98854</v>
       </c>
       <c r="D3" t="n">
-        <v>16.58481</v>
+        <v>16.76764</v>
       </c>
       <c r="E3" t="n">
-        <v>16.60945</v>
+        <v>16.78809</v>
       </c>
       <c r="F3" t="n">
-        <v>42.81946</v>
+        <v>42.00743</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05063</v>
+        <v>0.05029</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81337</v>
+        <v>1.82376</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.69274</v>
+        <v>17.11051</v>
       </c>
       <c r="D4" t="n">
-        <v>16.49725</v>
+        <v>16.44904</v>
       </c>
       <c r="E4" t="n">
-        <v>16.80053</v>
+        <v>16.63089</v>
       </c>
       <c r="F4" t="n">
-        <v>42.7043</v>
+        <v>42.66381</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05129</v>
+        <v>0.05065</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81012</v>
+        <v>1.81639</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.57899</v>
+        <v>16.31474</v>
       </c>
       <c r="D6" t="n">
-        <v>15.72185</v>
+        <v>16.06781</v>
       </c>
       <c r="E6" t="n">
-        <v>16.55624</v>
+        <v>16.18482</v>
       </c>
       <c r="F6" t="n">
-        <v>22.34399</v>
+        <v>22.02279</v>
       </c>
       <c r="G6" t="n">
-        <v>34.00461</v>
+        <v>34.1893</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.77377</v>
+        <v>16.54456</v>
       </c>
       <c r="D7" t="n">
-        <v>15.98818</v>
+        <v>15.9333</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32241</v>
+        <v>16.512</v>
       </c>
       <c r="F7" t="n">
-        <v>21.35183</v>
+        <v>21.38061</v>
       </c>
       <c r="G7" t="n">
-        <v>34.89359</v>
+        <v>33.73801</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.41219</v>
+        <v>16.68064</v>
       </c>
       <c r="D8" t="n">
-        <v>15.91145</v>
+        <v>15.71694</v>
       </c>
       <c r="E8" t="n">
-        <v>16.28442</v>
+        <v>16.16874</v>
       </c>
       <c r="F8" t="n">
-        <v>21.75533</v>
+        <v>22.07421</v>
       </c>
       <c r="G8" t="n">
-        <v>34.10213</v>
+        <v>34.19202</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5962</v>
+        <v>0.61307</v>
       </c>
       <c r="D10" t="n">
-        <v>1.11327</v>
+        <v>1.13333</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.59942</v>
+        <v>0.59892</v>
       </c>
       <c r="D11" t="n">
-        <v>1.09765</v>
+        <v>1.12348</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.61268</v>
+        <v>0.59102</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12523</v>
+        <v>1.10733</v>
       </c>
     </row>
   </sheetData>
